--- a/data/file_generation/input/data_342/訂單明細_20251210-20251210_desensitized.xlsx
+++ b/data/file_generation/input/data_342/訂單明細_20251210-20251210_desensitized.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tianjiaojiao/Desktop/田姣姣/input/data_342/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95186A3C-74A0-8E4E-A1F7-A520DEF985BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD39FE1-DEDC-BE4C-A09C-35D6CBCBA099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="22020" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34600" yWindow="2720" windowWidth="22020" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="152">
   <si>
     <t>訂單編號</t>
   </si>
@@ -178,48 +178,21 @@
     <t>************</t>
   </si>
   <si>
-    <t>来一桶香辣牛肉桶面</t>
-  </si>
-  <si>
     <t>卤蛋</t>
   </si>
   <si>
-    <t>星选咖啡拿铁咖啡饮料</t>
-  </si>
-  <si>
-    <t>零度无糖可乐摩登罐</t>
-  </si>
-  <si>
     <t>香脆面奥尔良鸡翅味</t>
   </si>
   <si>
     <t>夹心饼干原味</t>
   </si>
   <si>
-    <t>牧场吐司</t>
-  </si>
-  <si>
     <t>青柠味维生素饮料</t>
   </si>
   <si>
-    <t>茉莉乌龙无糖</t>
-  </si>
-  <si>
-    <t>百岁山矿泉水</t>
-  </si>
-  <si>
-    <t>美汁源果粒橙</t>
-  </si>
-  <si>
     <t>冰红茶饮料</t>
   </si>
   <si>
-    <t>果滋果心青葡萄味</t>
-  </si>
-  <si>
-    <t>水特运动饮料</t>
-  </si>
-  <si>
     <t>维生素功能饮料</t>
   </si>
   <si>
@@ -464,6 +437,58 @@
   </si>
   <si>
     <t>2025-12-10 21:23:04</t>
+  </si>
+  <si>
+    <t>吐司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>干脆面烧烤鸡肉味</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>维生素功能饮料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌龙无糖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>矿泉水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>果粒橙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无糖可乐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青葡萄味</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青柠味维生素饮料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拿铁咖啡饮料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运动饮料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>香辣牛肉桶面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可乐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -542,14 +567,14 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -859,55 +884,56 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
+    <col min="6" max="6" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" ht="31" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-    </row>
-    <row r="2" spans="1:11" s="3" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="31" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" spans="1:11" s="2" customFormat="1" ht="20.25" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -928,22 +954,22 @@
         <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -963,22 +989,22 @@
         <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J4" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K4" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -998,22 +1024,22 @@
         <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I5" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J5" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="K5" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1033,22 +1059,22 @@
         <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" t="s">
         <v>70</v>
-      </c>
-      <c r="I6" t="s">
-        <v>72</v>
-      </c>
-      <c r="J6" t="s">
-        <v>78</v>
-      </c>
-      <c r="K6" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1068,22 +1094,22 @@
         <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7" t="s">
         <v>72</v>
-      </c>
-      <c r="J7" t="s">
-        <v>80</v>
-      </c>
-      <c r="K7" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1103,22 +1129,22 @@
         <v>51</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I8" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J8" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1138,22 +1164,22 @@
         <v>51</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G9">
         <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I9" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1173,22 +1199,22 @@
         <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I10" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J10" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="K10" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1208,22 +1234,22 @@
         <v>51</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I11" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J11" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="K11" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1243,22 +1269,22 @@
         <v>51</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I12" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J12" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K12" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1278,22 +1304,22 @@
         <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I13" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J13" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K13" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1313,22 +1339,22 @@
         <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I14" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J14" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K14" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1348,22 +1374,22 @@
         <v>51</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I15" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J15" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K15" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1383,22 +1409,22 @@
         <v>51</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I16" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J16" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K16" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1418,22 +1444,22 @@
         <v>51</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I17" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J17" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K17" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1453,22 +1479,22 @@
         <v>51</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I18" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J18" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K18" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1488,22 +1514,22 @@
         <v>51</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I19" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J19" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K19" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1523,22 +1549,22 @@
         <v>51</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="G20">
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I20" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J20" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K20" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1558,22 +1584,22 @@
         <v>51</v>
       </c>
       <c r="F21" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I21" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J21" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="K21" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1593,22 +1619,22 @@
         <v>51</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G22">
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I22" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J22" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="K22" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1628,22 +1654,22 @@
         <v>51</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I23" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J23" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="K23" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1663,22 +1689,22 @@
         <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I24" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J24" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1698,22 +1724,22 @@
         <v>51</v>
       </c>
       <c r="F25" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G25">
         <v>2</v>
       </c>
       <c r="H25" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I25" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J25" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1733,22 +1759,22 @@
         <v>51</v>
       </c>
       <c r="F26" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="G26">
         <v>4</v>
       </c>
       <c r="H26" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I26" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J26" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="K26" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1768,22 +1794,22 @@
         <v>51</v>
       </c>
       <c r="F27" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="G27">
         <v>3</v>
       </c>
       <c r="H27" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I27" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J27" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1803,22 +1829,22 @@
         <v>51</v>
       </c>
       <c r="F28" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I28" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J28" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="K28" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1838,22 +1864,22 @@
         <v>51</v>
       </c>
       <c r="F29" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I29" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J29" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="K29" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1873,22 +1899,22 @@
         <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I30" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J30" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="K30" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1908,22 +1934,22 @@
         <v>51</v>
       </c>
       <c r="F31" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I31" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J31" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="K31" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1943,22 +1969,22 @@
         <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I32" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J32" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="K32" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1978,22 +2004,22 @@
         <v>51</v>
       </c>
       <c r="F33" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I33" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J33" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="K33" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2013,22 +2039,22 @@
         <v>51</v>
       </c>
       <c r="F34" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I34" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J34" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="K34" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2048,22 +2074,22 @@
         <v>51</v>
       </c>
       <c r="F35" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G35">
         <v>2</v>
       </c>
       <c r="H35" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I35" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J35" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="K35" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2083,22 +2109,22 @@
         <v>51</v>
       </c>
       <c r="F36" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I36" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J36" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="K36" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2118,22 +2144,22 @@
         <v>51</v>
       </c>
       <c r="F37" t="s">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I37" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J37" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="K37" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2153,22 +2179,22 @@
         <v>51</v>
       </c>
       <c r="F38" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I38" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J38" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="K38" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2188,22 +2214,22 @@
         <v>51</v>
       </c>
       <c r="F39" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="G39">
         <v>5</v>
       </c>
       <c r="H39" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I39" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J39" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="K39" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2223,22 +2249,22 @@
         <v>51</v>
       </c>
       <c r="F40" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="G40">
         <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I40" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J40" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="K40" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2258,22 +2284,22 @@
         <v>51</v>
       </c>
       <c r="F41" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G41">
         <v>2</v>
       </c>
       <c r="H41" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I41" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J41" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="K41" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2293,22 +2319,22 @@
         <v>51</v>
       </c>
       <c r="F42" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="G42">
         <v>3</v>
       </c>
       <c r="H42" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I42" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J42" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="K42" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2328,22 +2354,22 @@
         <v>51</v>
       </c>
       <c r="F43" t="s">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="G43">
         <v>3</v>
       </c>
       <c r="H43" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I43" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J43" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="K43" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2363,22 +2389,22 @@
         <v>51</v>
       </c>
       <c r="F44" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G44">
         <v>3</v>
       </c>
       <c r="H44" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I44" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J44" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="K44" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2398,22 +2424,22 @@
         <v>51</v>
       </c>
       <c r="F45" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G45">
         <v>3</v>
       </c>
       <c r="H45" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I45" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J45" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="K45" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -2433,22 +2459,22 @@
         <v>51</v>
       </c>
       <c r="F46" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I46" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J46" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="K46" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -2468,22 +2494,22 @@
         <v>51</v>
       </c>
       <c r="F47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G47">
         <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I47" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J47" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="K47" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2503,22 +2529,22 @@
         <v>51</v>
       </c>
       <c r="F48" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="G48">
         <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I48" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J48" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="K48" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2538,22 +2564,22 @@
         <v>51</v>
       </c>
       <c r="F49" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="G49">
         <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I49" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J49" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="K49" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2573,22 +2599,22 @@
         <v>51</v>
       </c>
       <c r="F50" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I50" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J50" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="K50" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2608,22 +2634,22 @@
         <v>51</v>
       </c>
       <c r="F51" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G51">
         <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I51" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J51" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="K51" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2643,22 +2669,22 @@
         <v>51</v>
       </c>
       <c r="F52" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I52" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J52" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="K52" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2678,22 +2704,22 @@
         <v>51</v>
       </c>
       <c r="F53" t="s">
-        <v>66</v>
+        <v>141</v>
       </c>
       <c r="G53">
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I53" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J53" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K53" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2713,22 +2739,22 @@
         <v>51</v>
       </c>
       <c r="F54" t="s">
-        <v>69</v>
+        <v>140</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I54" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J54" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K54" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2748,22 +2774,22 @@
         <v>51</v>
       </c>
       <c r="F55" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="G55">
         <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I55" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J55" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="K55" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -2783,22 +2809,22 @@
         <v>51</v>
       </c>
       <c r="F56" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I56" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J56" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="K56" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -2818,22 +2844,22 @@
         <v>51</v>
       </c>
       <c r="F57" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I57" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J57" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="K57" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -3009,13 +3035,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7438661-5B0B-4A69-B7B2-1FA3A7E41F81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8484407-612D-4A33-B686-4EF88EC2F295}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAAE4351-D732-44F9-87AD-A80ED44473DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{404B61F8-67BD-45F3-9980-720D6E7B9E2A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12A5D79B-2F1E-40C8-8104-75F99614AAF2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AFEB4A7-E0EA-4712-945D-0B1BC2D48CA9}"/>
 </file>